--- a/back/candidate-evaluations.xlsx
+++ b/back/candidate-evaluations.xlsx
@@ -199,9 +199,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -516,71 +515,71 @@
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.005" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.005" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.005" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.005" style="2" customWidth="1"/>
-    <col min="5" max="5" width="18.005" style="2" customWidth="1"/>
-    <col min="6" max="6" width="16.005" style="1" customWidth="1"/>
-    <col min="7" max="8" width="60.005" style="1" customWidth="1"/>
-    <col min="9" max="9" width="80.005" style="1" customWidth="1"/>
+    <col min="1" max="1" width="24.005" customWidth="1"/>
+    <col min="2" max="2" width="28.005" customWidth="1"/>
+    <col min="3" max="3" width="10.005" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.005" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.005" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.005" customWidth="1"/>
+    <col min="7" max="8" width="60.005" customWidth="1"/>
+    <col min="9" max="9" width="80.005" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" ht="1035.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <v>100</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <v>5</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>157</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>14</v>
       </c>
     </row>
